--- a/informes_data/Tercera FEB/2025-26/Regular_Season/aggregate_individual/AGG_IND_BYSPANIA TÍJOLA.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/aggregate_individual/AGG_IND_BYSPANIA TÍJOLA.xlsx
@@ -553,7 +553,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>E. KOYANOUBA DJIRANGAYE</t>
+          <t>L. RUEDA SANTAELLA</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -565,73 +565,73 @@
         <v>26</v>
       </c>
       <c r="D2" t="n">
-        <v>121.3164</v>
+        <v>100.2338</v>
       </c>
       <c r="E2" t="n">
-        <v>86.46550000000001</v>
+        <v>77.22500000000001</v>
       </c>
       <c r="F2" t="n">
-        <v>34.8507</v>
+        <v>23.0089</v>
       </c>
       <c r="G2" t="n">
-        <v>17.9037</v>
+        <v>24.1187</v>
       </c>
       <c r="H2" t="n">
-        <v>26.5005</v>
+        <v>27.613</v>
       </c>
       <c r="I2" t="n">
-        <v>-8.5968</v>
+        <v>-3.4944</v>
       </c>
       <c r="J2" t="n">
-        <v>39.3188</v>
+        <v>60.2087</v>
       </c>
       <c r="K2" t="n">
-        <v>38.3741</v>
+        <v>43.8009</v>
       </c>
       <c r="L2" t="n">
-        <v>0.9448000000000003</v>
+        <v>16.4081</v>
       </c>
       <c r="M2" t="n">
-        <v>-21.415</v>
+        <v>-36.0902</v>
       </c>
       <c r="N2" t="n">
-        <v>-11.8737</v>
+        <v>-16.1877</v>
       </c>
       <c r="O2" t="n">
-        <v>-9.5418</v>
+        <v>-19.9022</v>
       </c>
       <c r="P2" t="n">
-        <v>5.5504</v>
+        <v>11.4972</v>
       </c>
       <c r="Q2" t="n">
-        <v>-46.1857</v>
+        <v>-44.0049</v>
       </c>
       <c r="R2" t="n">
-        <v>51.7364</v>
+        <v>55.5025</v>
       </c>
       <c r="S2" t="n">
-        <v>63.6809</v>
+        <v>22.5764</v>
       </c>
       <c r="T2" t="n">
-        <v>43.3832</v>
+        <v>13.2045</v>
       </c>
       <c r="U2" t="n">
-        <v>20.2976</v>
+        <v>9.371699999999999</v>
       </c>
       <c r="V2" t="n">
-        <v>34.1816</v>
+        <v>42.0417</v>
       </c>
       <c r="W2" t="n">
-        <v>49.9492</v>
+        <v>47.8168</v>
       </c>
       <c r="X2" t="n">
-        <v>-15.768</v>
+        <v>-5.7751</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>L. RUEDA SANTAELLA</t>
+          <t>E. KOYANOUBA DJIRANGAYE</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,73 +643,73 @@
         <v>26</v>
       </c>
       <c r="D3" t="n">
-        <v>88.7094</v>
+        <v>95.9008</v>
       </c>
       <c r="E3" t="n">
-        <v>70.74249999999999</v>
+        <v>65.4996</v>
       </c>
       <c r="F3" t="n">
-        <v>17.967</v>
+        <v>30.4011</v>
       </c>
       <c r="G3" t="n">
-        <v>24.1187</v>
+        <v>17.9037</v>
       </c>
       <c r="H3" t="n">
-        <v>27.613</v>
+        <v>26.5005</v>
       </c>
       <c r="I3" t="n">
-        <v>-3.4944</v>
+        <v>-8.5968</v>
       </c>
       <c r="J3" t="n">
-        <v>60.2087</v>
+        <v>39.3188</v>
       </c>
       <c r="K3" t="n">
-        <v>43.8009</v>
+        <v>38.3741</v>
       </c>
       <c r="L3" t="n">
-        <v>16.4081</v>
+        <v>0.9448000000000003</v>
       </c>
       <c r="M3" t="n">
-        <v>-36.0902</v>
+        <v>-21.415</v>
       </c>
       <c r="N3" t="n">
-        <v>-16.1877</v>
+        <v>-11.8737</v>
       </c>
       <c r="O3" t="n">
-        <v>-19.9022</v>
+        <v>-9.5418</v>
       </c>
       <c r="P3" t="n">
-        <v>11.4972</v>
+        <v>5.5504</v>
       </c>
       <c r="Q3" t="n">
-        <v>-44.0049</v>
+        <v>-46.1857</v>
       </c>
       <c r="R3" t="n">
-        <v>55.5025</v>
+        <v>51.7364</v>
       </c>
       <c r="S3" t="n">
-        <v>11.0521</v>
+        <v>38.2654</v>
       </c>
       <c r="T3" t="n">
-        <v>6.722</v>
+        <v>22.4173</v>
       </c>
       <c r="U3" t="n">
-        <v>4.3301</v>
+        <v>15.8483</v>
       </c>
       <c r="V3" t="n">
-        <v>42.0417</v>
+        <v>34.1816</v>
       </c>
       <c r="W3" t="n">
-        <v>47.8168</v>
+        <v>49.9492</v>
       </c>
       <c r="X3" t="n">
-        <v>-5.7751</v>
+        <v>-15.768</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>C. BELEMENE DZABATOU</t>
+          <t>E. DOMENECH ANTE</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -718,70 +718,70 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="D4" t="n">
-        <v>50.6599</v>
+        <v>58.251</v>
       </c>
       <c r="E4" t="n">
-        <v>42.5709</v>
+        <v>35.6408</v>
       </c>
       <c r="F4" t="n">
-        <v>8.089200000000002</v>
+        <v>22.6104</v>
       </c>
       <c r="G4" t="n">
-        <v>17.8137</v>
+        <v>39.5347</v>
       </c>
       <c r="H4" t="n">
-        <v>23.9938</v>
+        <v>25.5851</v>
       </c>
       <c r="I4" t="n">
-        <v>-6.179900000000002</v>
+        <v>13.9495</v>
       </c>
       <c r="J4" t="n">
-        <v>39.0257</v>
+        <v>67.9098</v>
       </c>
       <c r="K4" t="n">
-        <v>30.4625</v>
+        <v>41.1371</v>
       </c>
       <c r="L4" t="n">
-        <v>8.5634</v>
+        <v>26.7731</v>
       </c>
       <c r="M4" t="n">
-        <v>-21.2118</v>
+        <v>-28.3751</v>
       </c>
       <c r="N4" t="n">
-        <v>-6.4688</v>
+        <v>-15.5519</v>
       </c>
       <c r="O4" t="n">
-        <v>-14.7433</v>
+        <v>-12.8233</v>
       </c>
       <c r="P4" t="n">
-        <v>-4.9556</v>
+        <v>-11.8933</v>
       </c>
       <c r="Q4" t="n">
-        <v>-45.7893</v>
+        <v>-69.3781</v>
       </c>
       <c r="R4" t="n">
-        <v>40.8341</v>
+        <v>57.4846</v>
       </c>
       <c r="S4" t="n">
-        <v>42.72640000000001</v>
+        <v>19.08</v>
       </c>
       <c r="T4" t="n">
-        <v>29.4625</v>
+        <v>7.565</v>
       </c>
       <c r="U4" t="n">
-        <v>13.2643</v>
+        <v>11.5149</v>
       </c>
       <c r="V4" t="n">
-        <v>-4.9251</v>
+        <v>11.53</v>
       </c>
       <c r="W4" t="n">
-        <v>19.8722</v>
+        <v>29.544</v>
       </c>
       <c r="X4" t="n">
-        <v>-24.7971</v>
+        <v>-18.014</v>
       </c>
     </row>
     <row r="5">
@@ -799,13 +799,13 @@
         <v>25</v>
       </c>
       <c r="D5" t="n">
-        <v>42.5018</v>
+        <v>46.7679</v>
       </c>
       <c r="E5" t="n">
-        <v>23.4379</v>
+        <v>28.2782</v>
       </c>
       <c r="F5" t="n">
-        <v>19.0633</v>
+        <v>18.4896</v>
       </c>
       <c r="G5" t="n">
         <v>5.518999999999999</v>
@@ -844,13 +844,13 @@
         <v>49.5559</v>
       </c>
       <c r="S5" t="n">
-        <v>9.414</v>
+        <v>13.6802</v>
       </c>
       <c r="T5" t="n">
-        <v>1.4607</v>
+        <v>6.3009</v>
       </c>
       <c r="U5" t="n">
-        <v>7.9533</v>
+        <v>7.3791</v>
       </c>
       <c r="V5" t="n">
         <v>12.702</v>
@@ -865,7 +865,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>E. DOMENECH ANTE</t>
+          <t>C. BELEMENE DZABATOU</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -874,70 +874,70 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="D6" t="n">
-        <v>39.1704</v>
+        <v>39.9763</v>
       </c>
       <c r="E6" t="n">
-        <v>21.7841</v>
+        <v>31.9561</v>
       </c>
       <c r="F6" t="n">
-        <v>17.3865</v>
+        <v>8.020100000000001</v>
       </c>
       <c r="G6" t="n">
-        <v>39.5347</v>
+        <v>17.8137</v>
       </c>
       <c r="H6" t="n">
-        <v>25.5851</v>
+        <v>23.9938</v>
       </c>
       <c r="I6" t="n">
-        <v>13.9495</v>
+        <v>-6.179900000000002</v>
       </c>
       <c r="J6" t="n">
-        <v>67.9098</v>
+        <v>39.0257</v>
       </c>
       <c r="K6" t="n">
-        <v>41.1371</v>
+        <v>30.4625</v>
       </c>
       <c r="L6" t="n">
-        <v>26.7731</v>
+        <v>8.5634</v>
       </c>
       <c r="M6" t="n">
-        <v>-28.3751</v>
+        <v>-21.2118</v>
       </c>
       <c r="N6" t="n">
-        <v>-15.5519</v>
+        <v>-6.4688</v>
       </c>
       <c r="O6" t="n">
-        <v>-12.8233</v>
+        <v>-14.7433</v>
       </c>
       <c r="P6" t="n">
-        <v>-11.8933</v>
+        <v>-4.9556</v>
       </c>
       <c r="Q6" t="n">
-        <v>-69.3781</v>
+        <v>-45.7893</v>
       </c>
       <c r="R6" t="n">
-        <v>57.4846</v>
+        <v>40.8341</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.001000000000000112</v>
+        <v>32.0426</v>
       </c>
       <c r="T6" t="n">
-        <v>-6.2918</v>
+        <v>18.8477</v>
       </c>
       <c r="U6" t="n">
-        <v>6.291</v>
+        <v>13.1951</v>
       </c>
       <c r="V6" t="n">
-        <v>11.53</v>
+        <v>-4.9251</v>
       </c>
       <c r="W6" t="n">
-        <v>29.544</v>
+        <v>19.8722</v>
       </c>
       <c r="X6" t="n">
-        <v>-18.014</v>
+        <v>-24.7971</v>
       </c>
     </row>
     <row r="7">
@@ -955,13 +955,13 @@
         <v>21</v>
       </c>
       <c r="D7" t="n">
-        <v>29.1058</v>
+        <v>28.2668</v>
       </c>
       <c r="E7" t="n">
-        <v>1.863</v>
+        <v>1.7902</v>
       </c>
       <c r="F7" t="n">
-        <v>27.2431</v>
+        <v>26.4766</v>
       </c>
       <c r="G7" t="n">
         <v>-1.6856</v>
@@ -1000,13 +1000,13 @@
         <v>36.8694</v>
       </c>
       <c r="S7" t="n">
-        <v>20.7414</v>
+        <v>19.9024</v>
       </c>
       <c r="T7" t="n">
-        <v>9.789099999999999</v>
+        <v>9.716699999999999</v>
       </c>
       <c r="U7" t="n">
-        <v>10.9522</v>
+        <v>10.1856</v>
       </c>
       <c r="V7" t="n">
         <v>-3.8255</v>
@@ -1033,13 +1033,13 @@
         <v>3</v>
       </c>
       <c r="D8" t="n">
-        <v>20.383</v>
+        <v>21.0138</v>
       </c>
       <c r="E8" t="n">
-        <v>9.3703</v>
+        <v>10.31</v>
       </c>
       <c r="F8" t="n">
-        <v>11.0126</v>
+        <v>10.7038</v>
       </c>
       <c r="G8" t="n">
         <v>10.8939</v>
@@ -1078,13 +1078,13 @@
         <v>8.9201</v>
       </c>
       <c r="S8" t="n">
-        <v>2.826</v>
+        <v>3.457</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.08029999999999993</v>
+        <v>0.8595</v>
       </c>
       <c r="U8" t="n">
-        <v>2.9063</v>
+        <v>2.5975</v>
       </c>
       <c r="V8" t="n">
         <v>3.8879</v>
@@ -1099,7 +1099,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>S. TORRECILLAS  LAJARA</t>
+          <t>C. ZULUAGA</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1108,70 +1108,70 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="D9" t="n">
-        <v>3.6241</v>
+        <v>6.712999999999999</v>
       </c>
       <c r="E9" t="n">
-        <v>3.6241</v>
+        <v>-4.6112</v>
       </c>
       <c r="F9" t="n">
-        <v>0</v>
+        <v>11.3243</v>
       </c>
       <c r="G9" t="n">
-        <v>3.6241</v>
+        <v>3.594099999999999</v>
       </c>
       <c r="H9" t="n">
-        <v>1.8161</v>
+        <v>-4.939500000000001</v>
       </c>
       <c r="I9" t="n">
-        <v>1.8081</v>
+        <v>8.533200000000003</v>
       </c>
       <c r="J9" t="n">
-        <v>3.6241</v>
+        <v>18.447</v>
       </c>
       <c r="K9" t="n">
-        <v>1.8161</v>
+        <v>6.1134</v>
       </c>
       <c r="L9" t="n">
-        <v>1.8081</v>
+        <v>12.3334</v>
       </c>
       <c r="M9" t="n">
-        <v>0</v>
+        <v>-14.853</v>
       </c>
       <c r="N9" t="n">
-        <v>0</v>
+        <v>-11.053</v>
       </c>
       <c r="O9" t="n">
-        <v>0</v>
+        <v>-3.8</v>
       </c>
       <c r="P9" t="n">
-        <v>0</v>
+        <v>-2.3785</v>
       </c>
       <c r="Q9" t="n">
-        <v>0</v>
+        <v>-33.4996</v>
       </c>
       <c r="R9" t="n">
-        <v>0</v>
+        <v>31.121</v>
       </c>
       <c r="S9" t="n">
-        <v>0</v>
+        <v>9.732699999999999</v>
       </c>
       <c r="T9" t="n">
-        <v>0</v>
+        <v>4.3507</v>
       </c>
       <c r="U9" t="n">
-        <v>0</v>
+        <v>5.3822</v>
       </c>
       <c r="V9" t="n">
-        <v>0</v>
+        <v>-4.234900000000001</v>
       </c>
       <c r="W9" t="n">
-        <v>0</v>
+        <v>6.0909</v>
       </c>
       <c r="X9" t="n">
-        <v>0</v>
+        <v>-10.3259</v>
       </c>
     </row>
     <row r="10">
@@ -1189,13 +1189,13 @@
         <v>17</v>
       </c>
       <c r="D10" t="n">
-        <v>2.767299999999999</v>
+        <v>4.862</v>
       </c>
       <c r="E10" t="n">
-        <v>6.794</v>
+        <v>6.744199999999999</v>
       </c>
       <c r="F10" t="n">
-        <v>-4.026899999999999</v>
+        <v>-1.8821</v>
       </c>
       <c r="G10" t="n">
         <v>-14.5324</v>
@@ -1234,13 +1234,13 @@
         <v>25.3728</v>
       </c>
       <c r="S10" t="n">
-        <v>10.9718</v>
+        <v>13.0667</v>
       </c>
       <c r="T10" t="n">
-        <v>8.837899999999999</v>
+        <v>8.7882</v>
       </c>
       <c r="U10" t="n">
-        <v>2.1336</v>
+        <v>4.2781</v>
       </c>
       <c r="V10" t="n">
         <v>-3.9794</v>
@@ -1255,7 +1255,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>R. CUBERO ROJANO</t>
+          <t>S. TORRECILLAS  LAJARA</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1264,76 +1264,76 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>25</v>
+        <v>7</v>
       </c>
       <c r="D11" t="n">
-        <v>0.1706000000000002</v>
+        <v>3.6241</v>
       </c>
       <c r="E11" t="n">
-        <v>-8.9648</v>
+        <v>3.6241</v>
       </c>
       <c r="F11" t="n">
-        <v>9.1356</v>
+        <v>0</v>
       </c>
       <c r="G11" t="n">
-        <v>-14.3286</v>
+        <v>3.6241</v>
       </c>
       <c r="H11" t="n">
-        <v>-5.490599999999999</v>
+        <v>1.8161</v>
       </c>
       <c r="I11" t="n">
-        <v>-8.837899999999999</v>
+        <v>1.8081</v>
       </c>
       <c r="J11" t="n">
-        <v>10.6986</v>
+        <v>3.6241</v>
       </c>
       <c r="K11" t="n">
-        <v>5.1267</v>
+        <v>1.8161</v>
       </c>
       <c r="L11" t="n">
-        <v>5.5715</v>
+        <v>1.8081</v>
       </c>
       <c r="M11" t="n">
-        <v>-25.0268</v>
+        <v>0</v>
       </c>
       <c r="N11" t="n">
-        <v>-10.6173</v>
+        <v>0</v>
       </c>
       <c r="O11" t="n">
-        <v>-14.4098</v>
+        <v>0</v>
       </c>
       <c r="P11" t="n">
-        <v>15.6595</v>
+        <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>-25.7688</v>
+        <v>0</v>
       </c>
       <c r="R11" t="n">
-        <v>41.4287</v>
+        <v>0</v>
       </c>
       <c r="S11" t="n">
-        <v>15.0792</v>
+        <v>0</v>
       </c>
       <c r="T11" t="n">
-        <v>5.0546</v>
+        <v>0</v>
       </c>
       <c r="U11" t="n">
-        <v>10.025</v>
+        <v>0</v>
       </c>
       <c r="V11" t="n">
-        <v>-16.2395</v>
+        <v>0</v>
       </c>
       <c r="W11" t="n">
-        <v>1.0513</v>
+        <v>0</v>
       </c>
       <c r="X11" t="n">
-        <v>-17.2907</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>G. MARTINEZ LAJARA</t>
+          <t>R. CUBERO ROJANO</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1342,76 +1342,76 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>3</v>
+        <v>25</v>
       </c>
       <c r="D12" t="n">
-        <v>-0.9456</v>
+        <v>1.3297</v>
       </c>
       <c r="E12" t="n">
-        <v>0.3007</v>
+        <v>-7.016800000000001</v>
       </c>
       <c r="F12" t="n">
-        <v>-1.2462</v>
+        <v>8.3462</v>
       </c>
       <c r="G12" t="n">
-        <v>-0.5866</v>
+        <v>-14.3286</v>
       </c>
       <c r="H12" t="n">
-        <v>-2.3391</v>
+        <v>-5.490599999999999</v>
       </c>
       <c r="I12" t="n">
-        <v>1.7526</v>
+        <v>-8.837899999999999</v>
       </c>
       <c r="J12" t="n">
-        <v>0.5502</v>
+        <v>10.6986</v>
       </c>
       <c r="K12" t="n">
-        <v>-0.659</v>
+        <v>5.1267</v>
       </c>
       <c r="L12" t="n">
-        <v>1.2092</v>
+        <v>5.5715</v>
       </c>
       <c r="M12" t="n">
-        <v>-1.1369</v>
+        <v>-25.0268</v>
       </c>
       <c r="N12" t="n">
-        <v>-1.6801</v>
+        <v>-10.6173</v>
       </c>
       <c r="O12" t="n">
-        <v>0.5433</v>
+        <v>-14.4098</v>
       </c>
       <c r="P12" t="n">
-        <v>0.1982</v>
+        <v>15.6595</v>
       </c>
       <c r="Q12" t="n">
-        <v>0</v>
+        <v>-25.7688</v>
       </c>
       <c r="R12" t="n">
-        <v>0.1982</v>
+        <v>41.4287</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.5572</v>
+        <v>16.2384</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.2496</v>
+        <v>7.0027</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.3076</v>
+        <v>9.235300000000001</v>
       </c>
       <c r="V12" t="n">
-        <v>0</v>
+        <v>-16.2395</v>
       </c>
       <c r="W12" t="n">
-        <v>0</v>
+        <v>1.0513</v>
       </c>
       <c r="X12" t="n">
-        <v>0</v>
+        <v>-17.2907</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>A. MARTOS BONACHELA</t>
+          <t>G. MARTINEZ LAJARA</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1420,61 +1420,61 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D13" t="n">
-        <v>-1.3836</v>
+        <v>-0.6517000000000001</v>
       </c>
       <c r="E13" t="n">
-        <v>-0.3587</v>
+        <v>0.4025</v>
       </c>
       <c r="F13" t="n">
-        <v>-1.0251</v>
+        <v>-1.0543</v>
       </c>
       <c r="G13" t="n">
-        <v>1.2274</v>
+        <v>-0.5866</v>
       </c>
       <c r="H13" t="n">
-        <v>-0.7279</v>
+        <v>-2.3391</v>
       </c>
       <c r="I13" t="n">
-        <v>1.9552</v>
+        <v>1.7526</v>
       </c>
       <c r="J13" t="n">
-        <v>2.6843</v>
+        <v>0.5502</v>
       </c>
       <c r="K13" t="n">
-        <v>1.9573</v>
+        <v>-0.659</v>
       </c>
       <c r="L13" t="n">
-        <v>0.7271</v>
+        <v>1.2092</v>
       </c>
       <c r="M13" t="n">
-        <v>-1.457</v>
+        <v>-1.1369</v>
       </c>
       <c r="N13" t="n">
-        <v>-2.6852</v>
+        <v>-1.6801</v>
       </c>
       <c r="O13" t="n">
-        <v>1.2281</v>
+        <v>0.5433</v>
       </c>
       <c r="P13" t="n">
-        <v>-2.1805</v>
+        <v>0.1982</v>
       </c>
       <c r="Q13" t="n">
-        <v>-2.9733</v>
+        <v>0</v>
       </c>
       <c r="R13" t="n">
-        <v>0.7927999999999999</v>
+        <v>0.1982</v>
       </c>
       <c r="S13" t="n">
-        <v>-0.4305</v>
+        <v>-0.2634</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.06970000000000001</v>
+        <v>-0.1477</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.3609</v>
+        <v>-0.1156</v>
       </c>
       <c r="V13" t="n">
         <v>0</v>
@@ -1489,7 +1489,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>L. GONZALEZ NAVARRETE</t>
+          <t>A. MARTOS BONACHELA</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1501,73 +1501,73 @@
         <v>4</v>
       </c>
       <c r="D14" t="n">
-        <v>-2.0408</v>
+        <v>-1.3285</v>
       </c>
       <c r="E14" t="n">
-        <v>-2.3624</v>
+        <v>-0.5</v>
       </c>
       <c r="F14" t="n">
-        <v>0.3217</v>
+        <v>-0.8286</v>
       </c>
       <c r="G14" t="n">
-        <v>-2.2664</v>
+        <v>1.2274</v>
       </c>
       <c r="H14" t="n">
-        <v>-1.4916</v>
+        <v>-0.7279</v>
       </c>
       <c r="I14" t="n">
-        <v>-0.7748</v>
+        <v>1.9552</v>
       </c>
       <c r="J14" t="n">
-        <v>-2.6158</v>
+        <v>2.6843</v>
       </c>
       <c r="K14" t="n">
-        <v>-1.2977</v>
+        <v>1.9573</v>
       </c>
       <c r="L14" t="n">
-        <v>-1.3181</v>
+        <v>0.7271</v>
       </c>
       <c r="M14" t="n">
-        <v>0.3493999999999999</v>
+        <v>-1.457</v>
       </c>
       <c r="N14" t="n">
-        <v>-0.1939</v>
+        <v>-2.6852</v>
       </c>
       <c r="O14" t="n">
-        <v>0.5433</v>
+        <v>1.2281</v>
       </c>
       <c r="P14" t="n">
-        <v>0.9911</v>
+        <v>-2.1805</v>
       </c>
       <c r="Q14" t="n">
-        <v>0</v>
+        <v>-2.9733</v>
       </c>
       <c r="R14" t="n">
-        <v>0.9911</v>
+        <v>0.7927999999999999</v>
       </c>
       <c r="S14" t="n">
-        <v>0.1046</v>
+        <v>-0.3753</v>
       </c>
       <c r="T14" t="n">
-        <v>0.2533000000000001</v>
+        <v>-0.2109</v>
       </c>
       <c r="U14" t="n">
-        <v>-0.1487</v>
+        <v>-0.1644</v>
       </c>
       <c r="V14" t="n">
-        <v>-0.8702000000000001</v>
+        <v>0</v>
       </c>
       <c r="W14" t="n">
         <v>0</v>
       </c>
       <c r="X14" t="n">
-        <v>-0.8702000000000001</v>
+        <v>0</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>C. ZULUAGA</t>
+          <t>L. GONZALEZ NAVARRETE</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1576,70 +1576,70 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>15</v>
+        <v>4</v>
       </c>
       <c r="D15" t="n">
-        <v>-2.595400000000001</v>
+        <v>-2.3225</v>
       </c>
       <c r="E15" t="n">
-        <v>-9.767299999999999</v>
+        <v>-2.5038</v>
       </c>
       <c r="F15" t="n">
-        <v>7.172</v>
+        <v>0.1812000000000001</v>
       </c>
       <c r="G15" t="n">
-        <v>3.594099999999999</v>
+        <v>-2.2664</v>
       </c>
       <c r="H15" t="n">
-        <v>-4.939500000000001</v>
+        <v>-1.4916</v>
       </c>
       <c r="I15" t="n">
-        <v>8.533200000000003</v>
+        <v>-0.7748</v>
       </c>
       <c r="J15" t="n">
-        <v>18.447</v>
+        <v>-2.6158</v>
       </c>
       <c r="K15" t="n">
-        <v>6.1134</v>
+        <v>-1.2977</v>
       </c>
       <c r="L15" t="n">
-        <v>12.3334</v>
+        <v>-1.3181</v>
       </c>
       <c r="M15" t="n">
-        <v>-14.853</v>
+        <v>0.3493999999999999</v>
       </c>
       <c r="N15" t="n">
-        <v>-11.053</v>
+        <v>-0.1939</v>
       </c>
       <c r="O15" t="n">
-        <v>-3.8</v>
+        <v>0.5433</v>
       </c>
       <c r="P15" t="n">
-        <v>-2.3785</v>
+        <v>0.9911</v>
       </c>
       <c r="Q15" t="n">
-        <v>-33.4996</v>
+        <v>0</v>
       </c>
       <c r="R15" t="n">
-        <v>31.121</v>
+        <v>0.9911</v>
       </c>
       <c r="S15" t="n">
-        <v>0.4246</v>
+        <v>-0.1771</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.8054000000000003</v>
+        <v>0.1121</v>
       </c>
       <c r="U15" t="n">
-        <v>1.2299</v>
+        <v>-0.2891</v>
       </c>
       <c r="V15" t="n">
-        <v>-4.234900000000001</v>
+        <v>-0.8702000000000001</v>
       </c>
       <c r="W15" t="n">
-        <v>6.0909</v>
+        <v>0</v>
       </c>
       <c r="X15" t="n">
-        <v>-10.3259</v>
+        <v>-0.8702000000000001</v>
       </c>
     </row>
     <row r="16">
@@ -1735,13 +1735,13 @@
         <v>5</v>
       </c>
       <c r="D17" t="n">
-        <v>-5.6706</v>
+        <v>-6.0052</v>
       </c>
       <c r="E17" t="n">
-        <v>-4.3244</v>
+        <v>-4.7715</v>
       </c>
       <c r="F17" t="n">
-        <v>-1.3461</v>
+        <v>-1.2338</v>
       </c>
       <c r="G17" t="n">
         <v>-3.9364</v>
@@ -1780,13 +1780,13 @@
         <v>0.9909999999999999</v>
       </c>
       <c r="S17" t="n">
-        <v>0.464</v>
+        <v>0.1295</v>
       </c>
       <c r="T17" t="n">
-        <v>0.9324</v>
+        <v>0.4856</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.4684</v>
+        <v>-0.356</v>
       </c>
       <c r="V17" t="n">
         <v>-1.2071</v>
@@ -1813,13 +1813,13 @@
         <v>23</v>
       </c>
       <c r="D18" t="n">
-        <v>-10.7084</v>
+        <v>-6.352200000000001</v>
       </c>
       <c r="E18" t="n">
-        <v>-11.7281</v>
+        <v>-9.0565</v>
       </c>
       <c r="F18" t="n">
-        <v>1.0193</v>
+        <v>2.704299999999999</v>
       </c>
       <c r="G18" t="n">
         <v>-10.9399</v>
@@ -1858,13 +1858,13 @@
         <v>13.8753</v>
       </c>
       <c r="S18" t="n">
-        <v>-1.692</v>
+        <v>2.6641</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.895</v>
+        <v>1.777</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.7973000000000001</v>
+        <v>0.8875</v>
       </c>
       <c r="V18" t="n">
         <v>-5.8072</v>
@@ -1891,13 +1891,13 @@
         <v>23</v>
       </c>
       <c r="D19" t="n">
-        <v>-12.8802</v>
+        <v>-8.604000000000001</v>
       </c>
       <c r="E19" t="n">
-        <v>-19.2977</v>
+        <v>-18.345</v>
       </c>
       <c r="F19" t="n">
-        <v>6.4175</v>
+        <v>9.741299999999999</v>
       </c>
       <c r="G19" t="n">
         <v>-11.3345</v>
@@ -1936,13 +1936,13 @@
         <v>23.9851</v>
       </c>
       <c r="S19" t="n">
-        <v>7.0008</v>
+        <v>11.2772</v>
       </c>
       <c r="T19" t="n">
-        <v>6.3306</v>
+        <v>7.2834</v>
       </c>
       <c r="U19" t="n">
-        <v>0.6699999999999997</v>
+        <v>3.9942</v>
       </c>
       <c r="V19" t="n">
         <v>-6.7629</v>
@@ -1969,13 +1969,13 @@
         <v>21</v>
       </c>
       <c r="D20" t="n">
-        <v>-16.974</v>
+        <v>-13.0454</v>
       </c>
       <c r="E20" t="n">
-        <v>-8.4709</v>
+        <v>-5.188</v>
       </c>
       <c r="F20" t="n">
-        <v>-8.503299999999999</v>
+        <v>-7.8573</v>
       </c>
       <c r="G20" t="n">
         <v>-9.122399999999999</v>
@@ -2014,13 +2014,13 @@
         <v>8.126999999999999</v>
       </c>
       <c r="S20" t="n">
-        <v>-4.782</v>
+        <v>-0.8533999999999999</v>
       </c>
       <c r="T20" t="n">
-        <v>-3.2775</v>
+        <v>0.005499999999999949</v>
       </c>
       <c r="U20" t="n">
-        <v>-1.5045</v>
+        <v>-0.8586</v>
       </c>
       <c r="V20" t="n">
         <v>-8.025399999999999</v>
@@ -2047,13 +2047,13 @@
         <v>26</v>
       </c>
       <c r="D21" t="n">
-        <v>342.335</v>
+        <v>365.7546</v>
       </c>
       <c r="E21" t="n">
-        <v>200.6231</v>
+        <v>208.4223</v>
       </c>
       <c r="F21" t="n">
-        <v>141.7114</v>
+        <v>157.3322</v>
       </c>
       <c r="G21" t="n">
         <v>54.8196</v>
@@ -2083,22 +2083,22 @@
         <v>-101.7907</v>
       </c>
       <c r="P21" t="n">
-        <v>63.4315</v>
+        <v>63.43150000000001</v>
       </c>
       <c r="Q21" t="n">
         <v>-384.55</v>
       </c>
       <c r="R21" t="n">
-        <v>447.9841999999999</v>
+        <v>447.9842</v>
       </c>
       <c r="S21" t="n">
-        <v>176.8249</v>
+        <v>200.2452</v>
       </c>
       <c r="T21" t="n">
-        <v>100.4322</v>
+        <v>108.2334</v>
       </c>
       <c r="U21" t="n">
-        <v>76.3925</v>
+        <v>92.01240000000001</v>
       </c>
       <c r="V21" t="n">
         <v>47.2589</v>
